--- a/examples/rpg/data/rpg.xlsx
+++ b/examples/rpg/data/rpg.xlsx
@@ -1,413 +1,1893 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" r:id="rId2"/>
-    <sheet name="Monster" sheetId="3" r:id="rId3"/>
-    <sheet name="DropTable" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Skill'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monster'!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DropTable'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Quest'!$A$1:$K$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Item ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Level Requirement</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stack Limit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Attributes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Elemental Bonus</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Upgrade Item ID</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Legacy Power</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>iron_sword</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Iron Sword</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>weapon | melee</t>
-        </is>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>x: 2.0, y: 3.0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>weapon | melee | starter</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>power: 12, durability: 80</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 12, Fire: 0</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>flame_staff</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Flame Staff</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>weapon | magic</t>
-        </is>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>x: 12.0, y: -4.5</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>weapon | magic | fire</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>power: 48, focus: 32</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 4, Fire: 70</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>meteor_staff</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>meteor_staff</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Meteor Staff</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>x: 15.0, y: -6.0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>weapon | magic | ultimate</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>power: 96, focus: 70</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 8, Fire: 120, Lightning: 30</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>phoenix_feather</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Phoenix Feather</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>material | revive</t>
-        </is>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>x: -8.0, y: 18.0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>material | revive | fire</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>power: 5, value: 100</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Fire: 40, Holy: 15</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>dragon_scale</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Dragon Scale</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>x: 32.0, y: 44.0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>armor | material | dragon</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>power: 110, defense: 140</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 20, Fire: 45, Shadow: 10</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="51" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Skill ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Follow Up ID</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Allowed Slots</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Targeting</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>slash</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Slash</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="2" t="n">
         <v>1.5</v>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>0 | 10 | 20</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon | Armor</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>shape: cone, params: {range: 2.0, angle: 90.0}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>fireball</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Fireball</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="D3">
+      <c r="E3" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>0 | 25 | 50</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon | Accessory</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>shape: circle, params: {range: 8.0, radius: 2.5}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>meteor</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Meteor</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="D4">
+      <c r="E4" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0 | 50 | 100</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>shape: circle, params: {range: 12.0, radius: 5.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>battle_trance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Battle Trance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0 | 5 | 10</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Weapon | Armor</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>shape: self, params: {range: 0.0, duration: 12.0}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Monster ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rarity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Skill ID</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Signature Item ID</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Abilities</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Phases</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spawn Points</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Flags</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>goblin_warrior</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Goblin Warrior</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>hp: 120, attack: 24, defense: 8, speed: 1.2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>hp: 120, attack: 24, defense: 8, speed: 1.2, crit: 5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>x: 10.0, y: 4.0</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 1.0, Fire: 0.8, Ice: 1.2</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>slash</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>iron_sword</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>{skill_id: slash, priority: 1, chance: 1.0}</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1: {region: forest, point: {x: 9.0, y: 4.0}, radius: 5.0, conditions: {day: 1, weather: 0}}</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>fire_mage</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Fire Mage</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>hp: 260, attack: 70, defense: 24, speed: 0.9</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>hp: 260, attack: 70, defense: 24, speed: 0.9, crit: 12</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>x: 22.0, y: -8.0</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 1.0, Fire: 0.4, Ice: 1.5, Shadow: 1.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>fireball</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>flame_staff</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>{skill_id: fireball, priority: 1, chance: 0.85} | {skill_id: battle_trance, priority: 2, chance: 1.0}</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1: {region: volcanic_keep, point: {x: 20.0, y: -7.0}, radius: 8.0, conditions: {day: 3, heat: 5}}, 2: {region: arcane_tower, point: {x: 25.0, y: -9.0}, radius: 4.0, conditions: {night: 1}}</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ancient_dragon</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Ancient Dragon</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>hp: 3000, attack: 320, defense: 180, speed: 0.7</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>hp: 3000, attack: 320, defense: 180, speed: 0.7, crit: 20</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>x: 60.0, y: 80.0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Physical: 0.8, Fire: 0.2, Ice: 1.8, Lightning: 1.0, Holy: 1.1, Shadow: 0.9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>meteor</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>dragon_scale</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>{skill_id: meteor, priority: 1, chance: 0.75} | {skill_id: fireball, priority: 2, chance: 0.95} | {skill_id: battle_trance, priority: 3, chance: 1.0}</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>{threshold_hp_pct: 0.5, added_skill_id: fireball, buffs: [Damage | Ultimate]} | {threshold_hp_pct: 0.2, added_skill_id: meteor, buffs: [Ultimate]}</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1: {region: dragon_peak, point: {x: 61.0, y: 79.0}, radius: 20.0, conditions: {day: 10, storm: 1}}, 3: {region: ancient_arena, point: {x: 80.0, y: 90.0}, radius: 15.0, conditions: {raid: 1}}</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Drop ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Monster ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rewards</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Weights</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bonus By Rarity</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Currency Curve</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Guaranteed Reward</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>drop_goblin_warrior</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>goblin_warrior</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[ItemReward{id: "reward_goblin_sword", item_id: iron_sword, count: 1} | CurrencyReward{id: "reward_goblin_gold", amount: 35}]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[70 | 30]</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>min_level: 1, required_element: Physical, flags: Damage</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: reward_goblin_sword, item_id: iron_sword, count: 1} | CurrencyReward{id: reward_goblin_gold, count: 1, currency: gold, amount: 35}</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>70 | 30</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Common: 0, Rare: 5</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1: 10, 5: 20</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>CurrencyReward{id: guaranteed_goblin_gold, count: 1, currency: gold, amount: 5}</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>tutorial | melee</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>drop_fire_mage</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>fire_mage</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[ItemReward{id: "reward_mage_staff", item_id: flame_staff, count: 1} | CurrencyReward{id: "reward_mage_gold", amount: 120}]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[25 | 75]</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>min_level: 12, required_element: Fire, flags: Damage</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: reward_mage_staff, item_id: flame_staff, count: 1} | CurrencyReward{id: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{id: reward_mage_skill, skill_id: fireball, required_level: 12}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>25 | 65 | 10</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Common: 0, Rare: 15, Epic: 30</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1: 25, 18: 90</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: guaranteed_mage_staff, item_id: flame_staff, count: 1}</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>caster | fire</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>drop_ancient_dragon</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>ancient_dragon</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[ItemReward{id: "reward_dragon_feather", item_id: phoenix_feather, count: 2} | CurrencyReward{id: "reward_dragon_gold", amount: 1000}]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[40 | 60]</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>min_level: 45, required_element: Fire, flags: Ultimate</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: reward_dragon_feather, item_id: phoenix_feather, count: 2} | CurrencyReward{id: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{id: reward_dragon_meteor, skill_id: meteor, required_level: 45}</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40 | 45 | 15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Common: 0, Rare: 30, Epic: 80, Legendary: 120</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1: 100, 50: 900</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: guaranteed_dragon_scale, item_id: dragon_scale, count: 1}</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>raid | dragon | endgame</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quest ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Min Level</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Monster ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reward Item ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Reward Preview</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>quest_first_blade</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>First Blade</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>goblin_warrior</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>iron_sword</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>_</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>{key: defeat_goblins, target_count: 3, counters: {kill: 3, collect: 0}}</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: preview_first_blade, item_id: iron_sword, count: 1}</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>start_day: 1, end_day: 30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>key: root, text: "Clear the road.", next: [{key: accept, text: "I will handle it."} | {key: decline, text: "Later."}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>quest_mage_trial</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Mage Trial</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>fire_mage</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>flame_staff</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>quest_first_blade</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>{key: defeat_mage, target_count: 1, counters: {kill: 1}} | {key: collect_focus, target_count: 2, counters: {collect: 2, kill: 0}}</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>SkillUnlockReward{id: preview_mage_skill, skill_id: fireball, required_level: 12}</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>start_day: 5, end_day: 45</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>key: root, text: "Prove your focus.", next: [{key: teach, text: "Show me the spell."}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>quest_dragon_raid</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Raid</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Dragon Raid</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ancient_dragon</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>dragon_scale</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>quest_first_blade | quest_mage_trial</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>{key: break_wings, target_count: 2, counters: {kill: 1, collect: 2}} | {key: survive_meteor, target_count: 1, counters: {kill: 1}}</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ItemReward{id: preview_dragon_scale, item_id: dragon_scale, count: 1}</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>start_day: 20, end_day: 90</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>key: root, text: "The peak is burning.", next: [{key: rally, text: "Gather the raid."} | {key: scout, text: "Find a safer path.", next: [{key: report, text: "Return before dawn."}]}]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/examples/rpg/data/rpg.xlsx
+++ b/examples/rpg/data/rpg.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="R83a3a9f0251f4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rab2afdf909aa468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R435d71cd97a24d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="R2daf1cdd47f04eec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="Rb92f5e04fc4a4b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="6" r:id="Ra9b068a8192d4869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="7" r:id="Rde5aed87c14e434f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="8" r:id="R2287d07ba6044627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop" sheetId="9" r:id="R848d3a4604444931"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="10" r:id="R0a29b38eb06a4966"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="R87fb21fcbe184267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R409d8e553d3248eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R70197c7a6df449d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="R3eb1531560b84788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="R8adb1b848f014950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="6" r:id="R88e4bb8164264a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="7" r:id="R8a225621140e4c90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="8" r:id="R456238f5e0fa4f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop" sheetId="9" r:id="Rad9a526580ef48c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="10" r:id="Rf08169e1ac044646"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,7 +432,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>item.iron_sword.name</x:v>
+        <x:v>item_iron_sword_name</x:v>
       </x:c>
       <x:c r="B2" t="str">
         <x:v>铁剑</x:v>
@@ -452,7 +452,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>item.flame_staff.name</x:v>
+        <x:v>item_flame_staff_name</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>焰火法杖</x:v>
@@ -472,7 +472,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>item.meteor_staff.name</x:v>
+        <x:v>item_meteor_staff_name</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>陨星法杖</x:v>
@@ -492,7 +492,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>item.dragon_guard.name</x:v>
+        <x:v>item_dragon_guard_name</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>龙鳞护甲</x:v>
@@ -512,7 +512,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>buff.burning.name</x:v>
+        <x:v>buff_burning_name</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>燃烧</x:v>
@@ -532,7 +532,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>buff.battle_focus.name</x:v>
+        <x:v>buff_battle_focus_name</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>战斗专注</x:v>
@@ -552,7 +552,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>buff.meteor_mark.name</x:v>
+        <x:v>buff_meteor_mark_name</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>陨星印记</x:v>
@@ -572,7 +572,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>stage.forest_road.name</x:v>
+        <x:v>stage_forest_road_name</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>林地道路</x:v>
@@ -592,7 +592,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
-        <x:v>stage.arcane_tower.name</x:v>
+        <x:v>stage_arcane_tower_name</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>秘法高塔</x:v>
@@ -612,7 +612,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
-        <x:v>stage.dragon_peak.name</x:v>
+        <x:v>stage_dragon_peak_name</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>龙巢峰顶</x:v>
@@ -632,7 +632,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>quest.first_blade.title</x:v>
+        <x:v>quest_first_blade_title</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>第一把剑</x:v>
@@ -652,7 +652,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>quest.mage_trial.title</x:v>
+        <x:v>quest_mage_trial_title</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>法师试炼</x:v>
@@ -672,7 +672,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>quest.dragon_raid.title</x:v>
+        <x:v>quest_dragon_raid_title</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>巨龙讨伐</x:v>
@@ -692,7 +692,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>shop.starter.name</x:v>
+        <x:v>shop_starter_name</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>新手补给</x:v>
@@ -712,7 +712,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>shop.arcane.name</x:v>
+        <x:v>shop_arcane_name</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>秘法商店</x:v>
@@ -732,7 +732,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>shop.raid.name</x:v>
+        <x:v>shop_raid_name</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>讨伐补给</x:v>
@@ -826,7 +826,7 @@
         <x:v>Iron Sword</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>item.iron_sword.name</x:v>
+        <x:v>@item_iron_sword_name</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>Common</x:v>
@@ -856,7 +856,7 @@
         <x:v>Physical: 12, Fire: 0</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>flame_staff</x:v>
+        <x:v>@flame_staff</x:v>
       </x:c>
       <x:c r="N2" t="n">
         <x:v>10</x:v>
@@ -885,7 +885,7 @@
         <x:v>Flame Staff</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>item.flame_staff.name</x:v>
+        <x:v>@item_flame_staff_name</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Rare</x:v>
@@ -915,7 +915,7 @@
         <x:v>Physical: 4, Fire: 70</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>meteor_staff</x:v>
+        <x:v>@meteor_staff</x:v>
       </x:c>
       <x:c r="N3" t="n">
         <x:v>55</x:v>
@@ -944,7 +944,7 @@
         <x:v>Meteor Staff</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>item.meteor_staff.name</x:v>
+        <x:v>@item_meteor_staff_name</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Epic</x:v>
@@ -1003,7 +1003,7 @@
         <x:v>Dragon Guard</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>item.dragon_guard.name</x:v>
+        <x:v>@item_dragon_guard_name</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>Epic</x:v>
@@ -1051,7 +1051,7 @@
         <x:v>1: 500, 2: 750, 3: 950</x:v>
       </x:c>
       <x:c r="S5" t="str">
-        <x:v>iron_sword</x:v>
+        <x:v>@iron_sword</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1109,7 +1109,7 @@
         <x:v>Burning</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>buff.burning.name</x:v>
+        <x:v>@buff_burning_name</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>Damage</x:v>
@@ -1147,7 +1147,7 @@
         <x:v>Battle Focus</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>buff.battle_focus.name</x:v>
+        <x:v>@buff_battle_focus_name</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Passive</x:v>
@@ -1185,7 +1185,7 @@
         <x:v>Meteor Mark</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>buff.meteor_mark.name</x:v>
+        <x:v>@buff_meteor_mark_name</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Ultimate</x:v>
@@ -1329,10 +1329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>slash</x:v>
+        <x:v>@slash</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>burning</x:v>
+        <x:v>@burning</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>0 | 25 | 50</x:v>
@@ -1370,10 +1370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>fireball</x:v>
+        <x:v>@fireball</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>meteor_mark</x:v>
+        <x:v>@meteor_mark</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>0 | 50 | 100</x:v>
@@ -1414,7 +1414,7 @@
         <x:v>_</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>battle_focus</x:v>
+        <x:v>@battle_focus</x:v>
       </x:c>
       <x:c r="J5" t="str">
         <x:v>0 | 5 | 10</x:v>
@@ -1502,13 +1502,13 @@
         <x:v>Physical: 1.0, Fire: 0.8, Ice: 1.2</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>slash</x:v>
+        <x:v>@slash</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>iron_sword</x:v>
+        <x:v>@iron_sword</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>{skill_id: slash, priority: 1, chance: 1.0}</x:v>
+        <x:v>{skill: @slash, priority: 1, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K2" t="str">
         <x:v>_</x:v>
@@ -1543,13 +1543,13 @@
         <x:v>Physical: 1.0, Fire: 0.4, Ice: 1.5, Shadow: 1.0</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>fireball</x:v>
+        <x:v>@fireball</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>flame_staff</x:v>
+        <x:v>@flame_staff</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>{skill_id: fireball, priority: 1, chance: 0.85} | {skill_id: battle_trance, priority: 2, chance: 1.0}</x:v>
+        <x:v>{skill: @fireball, priority: 1, chance: 0.85} | {skill: @battle_trance, priority: 2, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K3" t="str">
         <x:v>_</x:v>
@@ -1584,16 +1584,16 @@
         <x:v>Physical: 0.8, Fire: 0.2, Ice: 1.8, Lightning: 1.0, Holy: 1.1, Shadow: 0.9</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>meteor</x:v>
+        <x:v>@meteor</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>dragon_scale</x:v>
+        <x:v>@dragon_scale</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>{skill_id: meteor, priority: 1, chance: 0.75} | {skill_id: fireball, priority: 2, chance: 0.95} | {skill_id: battle_trance, priority: 3, chance: 1.0}</x:v>
+        <x:v>{skill: @meteor, priority: 1, chance: 0.75} | {skill: @fireball, priority: 2, chance: 0.95} | {skill: @battle_trance, priority: 3, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>{threshold_hp_pct: 0.5, added_skill_id: fireball, buffs: [Damage | Ultimate]} | {threshold_hp_pct: 0.2, added_skill_id: meteor, buffs: [Ultimate]}</x:v>
+        <x:v>{threshold_hp_pct: 0.5, added_skill: @fireball, buffs: [Damage | Ultimate]} | {threshold_hp_pct: 0.2, added_skill: @meteor, buffs: [Ultimate]}</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>1: {region: dragon_peak, point: {x: 61.0, y: 79.0}, radius: 20.0, conditions: {day: 10, storm: 1}}, 3: {region: ancient_arena, point: {x: 80.0, y: 90.0}, radius: 15.0, conditions: {raid: 1}}</x:v>
@@ -1645,13 +1645,13 @@
         <x:v>drop_goblin_warrior</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>goblin_warrior</x:v>
+        <x:v>@goblin_warrior</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>min_level: 1, required_element: Physical, flags: Damage</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>ItemReward{id: reward_goblin_sword, item_id: iron_sword, count: 1} | CurrencyReward{id: reward_goblin_gold, count: 1, currency: gold, amount: 35}</x:v>
+        <x:v>ItemReward{key: reward_goblin_sword, item: @iron_sword, count: 1} | CurrencyReward{key: reward_goblin_gold, count: 1, currency: gold, amount: 35}</x:v>
       </x:c>
       <x:c r="E2" t="str">
         <x:v>70 | 30</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>1: 10, 5: 20</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>CurrencyReward{id: guaranteed_goblin_gold, count: 1, currency: gold, amount: 5}</x:v>
+        <x:v>CurrencyReward{key: guaranteed_goblin_gold, count: 1, currency: gold, amount: 5}</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>tutorial | melee</x:v>
@@ -1674,13 +1674,13 @@
         <x:v>drop_fire_mage</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>fire_mage</x:v>
+        <x:v>@fire_mage</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>min_level: 12, required_element: Fire, flags: Damage</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>ItemReward{id: reward_mage_staff, item_id: flame_staff, count: 1} | CurrencyReward{id: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{id: reward_mage_skill, skill_id: fireball, required_level: 12}</x:v>
+        <x:v>ItemReward{key: reward_mage_staff, item: @flame_staff, count: 1} | CurrencyReward{key: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{key: reward_mage_skill, skill: @fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>25 | 65 | 10</x:v>
@@ -1692,7 +1692,7 @@
         <x:v>1: 25, 18: 90</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>ItemReward{id: guaranteed_mage_staff, item_id: flame_staff, count: 1}</x:v>
+        <x:v>ItemReward{key: guaranteed_mage_staff, item: @flame_staff, count: 1}</x:v>
       </x:c>
       <x:c r="I3" t="str">
         <x:v>caster | fire</x:v>
@@ -1703,13 +1703,13 @@
         <x:v>drop_ancient_dragon</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ancient_dragon</x:v>
+        <x:v>@ancient_dragon</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>min_level: 45, required_element: Fire, flags: Ultimate</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>ItemReward{id: reward_dragon_feather, item_id: phoenix_feather, count: 2} | CurrencyReward{id: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{id: reward_dragon_meteor, skill_id: meteor, required_level: 45}</x:v>
+        <x:v>ItemReward{key: reward_dragon_feather, item: @phoenix_feather, count: 2} | CurrencyReward{key: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{key: reward_dragon_meteor, skill: @meteor, required_level: 45}</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>40 | 45 | 15</x:v>
@@ -1721,7 +1721,7 @@
         <x:v>1: 100, 50: 900</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>ItemReward{id: guaranteed_dragon_scale, item_id: dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: guaranteed_dragon_scale, item: @dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>raid | dragon | endgame</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>stage_forest_road</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>stage.forest_road.name</x:v>
+        <x:v>@stage_forest_road_name</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>Story</x:v>
@@ -1788,13 +1788,13 @@
         <x:v>{x: 9.0, y: 4.0}</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>{monster_id: goblin_warrior, count: 3, level_offset: 0, weight: 100}</x:v>
+        <x:v>{monster: @goblin_warrior, count: 3, level_offset: 0, weight: 100}</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>drop_goblin_warrior</x:v>
+        <x:v>@drop_goblin_warrior</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>ItemReward{id: first_clear_forest_blade, item_id: iron_sword, count: 1}</x:v>
+        <x:v>ItemReward{key: first_clear_forest_blade, item: @iron_sword, count: 1}</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>stamina: 6, time_limit: 300</x:v>
@@ -1805,7 +1805,7 @@
         <x:v>stage_arcane_tower</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>stage.arcane_tower.name</x:v>
+        <x:v>@stage_arcane_tower_name</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Elite</x:v>
@@ -1820,13 +1820,13 @@
         <x:v>{x: 20.0, y: -7.0} | {x: 25.0, y: -9.0}</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>{monster_id: fire_mage, count: 1, level_offset: 0, weight: 70} | {monster_id: goblin_warrior, count: 2, level_offset: 3, weight: 30}</x:v>
+        <x:v>{monster: @fire_mage, count: 1, level_offset: 0, weight: 70} | {monster: @goblin_warrior, count: 2, level_offset: 3, weight: 30}</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>drop_fire_mage</x:v>
+        <x:v>@drop_fire_mage</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>SkillUnlockReward{id: first_clear_fireball, skill_id: fireball, required_level: 12}</x:v>
+        <x:v>SkillUnlockReward{key: first_clear_fireball, skill: @fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>stamina: 12, time_limit: 420</x:v>
@@ -1837,7 +1837,7 @@
         <x:v>stage_dragon_peak</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>stage.dragon_peak.name</x:v>
+        <x:v>@stage_dragon_peak_name</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Raid</x:v>
@@ -1852,13 +1852,13 @@
         <x:v>{x: 61.0, y: 79.0} | {x: 80.0, y: 90.0}</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>{monster_id: ancient_dragon, count: 1, level_offset: 0, weight: 100} | {monster_id: fire_mage, count: 2, level_offset: 5, weight: 20}</x:v>
+        <x:v>{monster: @ancient_dragon, count: 1, level_offset: 0, weight: 100} | {monster: @fire_mage, count: 2, level_offset: 5, weight: 20}</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>drop_ancient_dragon</x:v>
+        <x:v>@drop_ancient_dragon</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>ItemReward{id: first_clear_dragon_scale, item_id: dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: first_clear_dragon_scale, item: @dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>stamina: 30, time_limit: 900, raid_size: 4</x:v>
@@ -1922,7 +1922,7 @@
         <x:v>Story</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>quest.first_blade.title</x:v>
+        <x:v>@quest_first_blade_title</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>First Blade</x:v>
@@ -1931,13 +1931,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>stage_forest_road</x:v>
+        <x:v>@stage_forest_road</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>goblin_warrior</x:v>
+        <x:v>@goblin_warrior</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>iron_sword</x:v>
+        <x:v>@iron_sword</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>_</x:v>
@@ -1946,7 +1946,7 @@
         <x:v>{key: defeat_goblins, target_count: 3, counters: {kill: 3, collect: 0}}</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>ItemReward{id: preview_first_blade, item_id: iron_sword, count: 1}</x:v>
+        <x:v>ItemReward{key: preview_first_blade, item: @iron_sword, count: 1}</x:v>
       </x:c>
       <x:c r="L2" t="str">
         <x:v>start_day: 1, end_day: 30</x:v>
@@ -1963,7 +1963,7 @@
         <x:v>Side</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>quest.mage_trial.title</x:v>
+        <x:v>@quest_mage_trial_title</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Mage Trial</x:v>
@@ -1972,13 +1972,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>stage_arcane_tower</x:v>
+        <x:v>@stage_arcane_tower</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>fire_mage</x:v>
+        <x:v>@fire_mage</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>flame_staff</x:v>
+        <x:v>@flame_staff</x:v>
       </x:c>
       <x:c r="I3" t="str">
         <x:v>quest_first_blade</x:v>
@@ -1987,7 +1987,7 @@
         <x:v>{key: defeat_mage, target_count: 1, counters: {kill: 1}} | {key: collect_focus, target_count: 2, counters: {collect: 2, kill: 0}}</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>SkillUnlockReward{id: preview_mage_skill, skill_id: fireball, required_level: 12}</x:v>
+        <x:v>SkillUnlockReward{key: preview_mage_skill, skill: @fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="L3" t="str">
         <x:v>start_day: 5, end_day: 45</x:v>
@@ -2004,7 +2004,7 @@
         <x:v>Raid</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>quest.dragon_raid.title</x:v>
+        <x:v>@quest_dragon_raid_title</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Dragon Raid</x:v>
@@ -2013,13 +2013,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>stage_dragon_peak</x:v>
+        <x:v>@stage_dragon_peak</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>ancient_dragon</x:v>
+        <x:v>@ancient_dragon</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>dragon_scale</x:v>
+        <x:v>@dragon_scale</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>quest_first_blade | quest_mage_trial</x:v>
@@ -2028,7 +2028,7 @@
         <x:v>{key: break_wings, target_count: 2, counters: {kill: 1, collect: 2}} | {key: survive_meteor, target_count: 1, counters: {kill: 1}}</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>ItemReward{id: preview_dragon_scale, item_id: dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: preview_dragon_scale, item: @dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>start_day: 20, end_day: 90</x:v>
@@ -2077,7 +2077,7 @@
         <x:v>shop_starter</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>shop.starter.name</x:v>
+        <x:v>@shop_starter_name</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>General</x:v>
@@ -2092,7 +2092,7 @@
         <x:v>_</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>{item_id: healing_potion, price: 35, stock: 20, unlock_level: 1, required_quest: _, discount_by_day: {1: 0, 7: 10}} | {item_id: iron_sword, price: 120, stock: 1, unlock_level: 1, required_quest: quest_first_blade, discount_by_day: {1: 0}}</x:v>
+        <x:v>{item: @healing_potion, price: 35, stock: 20, unlock_level: 1, required_quest: _, discount_by_day: {1: 0, 7: 10}} | {item: @iron_sword, price: 120, stock: 1, unlock_level: 1, required_quest: @quest_first_blade, discount_by_day: {1: 0}}</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>gold</x:v>
@@ -2103,7 +2103,7 @@
         <x:v>shop_arcane</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>shop.arcane.name</x:v>
+        <x:v>@shop_arcane_name</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Event</x:v>
@@ -2115,10 +2115,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>stage_arcane_tower</x:v>
+        <x:v>@stage_arcane_tower</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>{item_id: flame_staff, price: 760, stock: 1, unlock_level: 12, required_quest: quest_mage_trial, discount_by_day: {1: 0, 14: 15}} | {item_id: phoenix_feather, price: 1800, stock: 5, unlock_level: 18, required_quest: quest_mage_trial, discount_by_day: {1: 0}}</x:v>
+        <x:v>{item: @flame_staff, price: 760, stock: 1, unlock_level: 12, required_quest: @quest_mage_trial, discount_by_day: {1: 0, 14: 15}} | {item: @phoenix_feather, price: 1800, stock: 5, unlock_level: 18, required_quest: @quest_mage_trial, discount_by_day: {1: 0}}</x:v>
       </x:c>
       <x:c r="H3" t="str">
         <x:v>gold | event_token</x:v>
@@ -2129,7 +2129,7 @@
         <x:v>shop_raid</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>shop.raid.name</x:v>
+        <x:v>@shop_raid_name</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Raid</x:v>
@@ -2141,10 +2141,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>stage_dragon_peak</x:v>
+        <x:v>@stage_dragon_peak</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>{item_id: dragon_scale, price: 5200, stock: 4, unlock_level: 45, required_quest: quest_dragon_raid, discount_by_day: {1: 0}} | {item_id: meteor_staff, price: 2600, stock: 1, unlock_level: 45, required_quest: quest_dragon_raid, discount_by_day: {1: 0, 30: 20}}</x:v>
+        <x:v>{item: @dragon_scale, price: 5200, stock: 4, unlock_level: 45, required_quest: @quest_dragon_raid, discount_by_day: {1: 0}} | {item: @meteor_staff, price: 2600, stock: 1, unlock_level: 45, required_quest: @quest_dragon_raid, discount_by_day: {1: 0, 30: 20}}</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>gold | raid_token</x:v>

--- a/examples/rpg/data/rpg.xlsx
+++ b/examples/rpg/data/rpg.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="R87fb21fcbe184267"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R409d8e553d3248eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R70197c7a6df449d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="R3eb1531560b84788"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="R8adb1b848f014950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="6" r:id="R88e4bb8164264a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="7" r:id="R8a225621140e4c90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="8" r:id="R456238f5e0fa4f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop" sheetId="9" r:id="Rad9a526580ef48c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="10" r:id="Rf08169e1ac044646"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="R52dbdc023bce415c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf531816d5cf84605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R68e2e336839d48c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="R2d8088a070354357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="R0be2e9de3b2f4d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="6" r:id="R3c95343529bf4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="7" r:id="R56856c5aa9744163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="8" r:id="R2e2443ebd0524bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop" sheetId="9" r:id="R15bab0945dcd4a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="10" r:id="Rdf3710ed718843a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -146,12 +146,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -826,7 +872,7 @@
         <x:v>Iron Sword</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>@item_iron_sword_name</x:v>
+        <x:v>@Text.item_iron_sword_name</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>Common</x:v>
@@ -856,7 +902,7 @@
         <x:v>Physical: 12, Fire: 0</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>@flame_staff</x:v>
+        <x:v>@Equipment.flame_staff</x:v>
       </x:c>
       <x:c r="N2" t="n">
         <x:v>10</x:v>
@@ -885,7 +931,7 @@
         <x:v>Flame Staff</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>@item_flame_staff_name</x:v>
+        <x:v>@Text.item_flame_staff_name</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Rare</x:v>
@@ -915,7 +961,7 @@
         <x:v>Physical: 4, Fire: 70</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>@meteor_staff</x:v>
+        <x:v>@Equipment.meteor_staff</x:v>
       </x:c>
       <x:c r="N3" t="n">
         <x:v>55</x:v>
@@ -944,7 +990,7 @@
         <x:v>Meteor Staff</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>@item_meteor_staff_name</x:v>
+        <x:v>@Text.item_meteor_staff_name</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Epic</x:v>
@@ -1003,7 +1049,7 @@
         <x:v>Dragon Guard</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>@item_dragon_guard_name</x:v>
+        <x:v>@Text.item_dragon_guard_name</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>Epic</x:v>
@@ -1051,7 +1097,7 @@
         <x:v>1: 500, 2: 750, 3: 950</x:v>
       </x:c>
       <x:c r="S5" t="str">
-        <x:v>@iron_sword</x:v>
+        <x:v>@Equipment.iron_sword</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1109,7 +1155,7 @@
         <x:v>Burning</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>@buff_burning_name</x:v>
+        <x:v>@Text.buff_burning_name</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>Damage</x:v>
@@ -1147,7 +1193,7 @@
         <x:v>Battle Focus</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>@buff_battle_focus_name</x:v>
+        <x:v>@Text.buff_battle_focus_name</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Passive</x:v>
@@ -1185,7 +1231,7 @@
         <x:v>Meteor Mark</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>@buff_meteor_mark_name</x:v>
+        <x:v>@Text.buff_meteor_mark_name</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Ultimate</x:v>
@@ -1329,10 +1375,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>@slash</x:v>
+        <x:v>@Skill.slash</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>@burning</x:v>
+        <x:v>@Buff.burning</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>0 | 25 | 50</x:v>
@@ -1370,10 +1416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>@fireball</x:v>
+        <x:v>@Skill.fireball</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>@meteor_mark</x:v>
+        <x:v>@Buff.meteor_mark</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>0 | 50 | 100</x:v>
@@ -1414,7 +1460,7 @@
         <x:v>_</x:v>
       </x:c>
       <x:c r="I5" t="str">
-        <x:v>@battle_focus</x:v>
+        <x:v>@Buff.battle_focus</x:v>
       </x:c>
       <x:c r="J5" t="str">
         <x:v>0 | 5 | 10</x:v>
@@ -1502,13 +1548,13 @@
         <x:v>Physical: 1.0, Fire: 0.8, Ice: 1.2</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>@slash</x:v>
+        <x:v>@Skill.slash</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>@iron_sword</x:v>
+        <x:v>@Equipment.iron_sword</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>{skill: @slash, priority: 1, chance: 1.0}</x:v>
+        <x:v>{skill: @Skill.slash, priority: 1, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K2" t="str">
         <x:v>_</x:v>
@@ -1543,13 +1589,13 @@
         <x:v>Physical: 1.0, Fire: 0.4, Ice: 1.5, Shadow: 1.0</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>@fireball</x:v>
+        <x:v>@Skill.fireball</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>@flame_staff</x:v>
+        <x:v>@Equipment.flame_staff</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>{skill: @fireball, priority: 1, chance: 0.85} | {skill: @battle_trance, priority: 2, chance: 1.0}</x:v>
+        <x:v>{skill: @Skill.fireball, priority: 1, chance: 0.85} | {skill: @Skill.battle_trance, priority: 2, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K3" t="str">
         <x:v>_</x:v>
@@ -1584,16 +1630,16 @@
         <x:v>Physical: 0.8, Fire: 0.2, Ice: 1.8, Lightning: 1.0, Holy: 1.1, Shadow: 0.9</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>@meteor</x:v>
+        <x:v>@Skill.meteor</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>@dragon_scale</x:v>
+        <x:v>@Item.dragon_scale</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>{skill: @meteor, priority: 1, chance: 0.75} | {skill: @fireball, priority: 2, chance: 0.95} | {skill: @battle_trance, priority: 3, chance: 1.0}</x:v>
+        <x:v>{skill: @Skill.meteor, priority: 1, chance: 0.75} | {skill: @Skill.fireball, priority: 2, chance: 0.95} | {skill: @Skill.battle_trance, priority: 3, chance: 1.0}</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>{threshold_hp_pct: 0.5, added_skill: @fireball, buffs: [Damage | Ultimate]} | {threshold_hp_pct: 0.2, added_skill: @meteor, buffs: [Ultimate]}</x:v>
+        <x:v>{threshold_hp_pct: 0.5, added_skill: @Skill.fireball, buffs: [Damage | Ultimate]} | {threshold_hp_pct: 0.2, added_skill: @Skill.meteor, buffs: [Ultimate]}</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>1: {region: dragon_peak, point: {x: 61.0, y: 79.0}, radius: 20.0, conditions: {day: 10, storm: 1}}, 3: {region: ancient_arena, point: {x: 80.0, y: 90.0}, radius: 15.0, conditions: {raid: 1}}</x:v>
@@ -1645,13 +1691,13 @@
         <x:v>drop_goblin_warrior</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>@goblin_warrior</x:v>
+        <x:v>@Monster.goblin_warrior</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>min_level: 1, required_element: Physical, flags: Damage</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>ItemReward{key: reward_goblin_sword, item: @iron_sword, count: 1} | CurrencyReward{key: reward_goblin_gold, count: 1, currency: gold, amount: 35}</x:v>
+        <x:v>ItemReward{key: reward_goblin_sword, item: @Equipment.iron_sword, count: 1} | CurrencyReward{key: reward_goblin_gold, count: 1, currency: gold, amount: 35}</x:v>
       </x:c>
       <x:c r="E2" t="str">
         <x:v>70 | 30</x:v>
@@ -1674,13 +1720,13 @@
         <x:v>drop_fire_mage</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>@fire_mage</x:v>
+        <x:v>@Monster.fire_mage</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>min_level: 12, required_element: Fire, flags: Damage</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>ItemReward{key: reward_mage_staff, item: @flame_staff, count: 1} | CurrencyReward{key: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{key: reward_mage_skill, skill: @fireball, required_level: 12}</x:v>
+        <x:v>ItemReward{key: reward_mage_staff, item: @Equipment.flame_staff, count: 1} | CurrencyReward{key: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{key: reward_mage_skill, skill: @Skill.fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>25 | 65 | 10</x:v>
@@ -1692,7 +1738,7 @@
         <x:v>1: 25, 18: 90</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>ItemReward{key: guaranteed_mage_staff, item: @flame_staff, count: 1}</x:v>
+        <x:v>ItemReward{key: guaranteed_mage_staff, item: @Equipment.flame_staff, count: 1}</x:v>
       </x:c>
       <x:c r="I3" t="str">
         <x:v>caster | fire</x:v>
@@ -1703,13 +1749,13 @@
         <x:v>drop_ancient_dragon</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>@ancient_dragon</x:v>
+        <x:v>@Monster.ancient_dragon</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>min_level: 45, required_element: Fire, flags: Ultimate</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>ItemReward{key: reward_dragon_feather, item: @phoenix_feather, count: 2} | CurrencyReward{key: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{key: reward_dragon_meteor, skill: @meteor, required_level: 45}</x:v>
+        <x:v>ItemReward{key: reward_dragon_feather, item: @Item.phoenix_feather, count: 2} | CurrencyReward{key: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{key: reward_dragon_meteor, skill: @Skill.meteor, required_level: 45}</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>40 | 45 | 15</x:v>
@@ -1721,7 +1767,7 @@
         <x:v>1: 100, 50: 900</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>ItemReward{key: guaranteed_dragon_scale, item: @dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: guaranteed_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>raid | dragon | endgame</x:v>
@@ -1773,7 +1819,7 @@
         <x:v>stage_forest_road</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>@stage_forest_road_name</x:v>
+        <x:v>@Text.stage_forest_road_name</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>Story</x:v>
@@ -1788,13 +1834,13 @@
         <x:v>{x: 9.0, y: 4.0}</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>{monster: @goblin_warrior, count: 3, level_offset: 0, weight: 100}</x:v>
+        <x:v>{monster: @Monster.goblin_warrior, count: 3, level_offset: 0, weight: 100}</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>@drop_goblin_warrior</x:v>
+        <x:v>@DropTable.drop_goblin_warrior</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>ItemReward{key: first_clear_forest_blade, item: @iron_sword, count: 1}</x:v>
+        <x:v>ItemReward{key: first_clear_forest_blade, item: @Equipment.iron_sword, count: 1}</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>stamina: 6, time_limit: 300</x:v>
@@ -1805,7 +1851,7 @@
         <x:v>stage_arcane_tower</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>@stage_arcane_tower_name</x:v>
+        <x:v>@Text.stage_arcane_tower_name</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Elite</x:v>
@@ -1820,13 +1866,13 @@
         <x:v>{x: 20.0, y: -7.0} | {x: 25.0, y: -9.0}</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>{monster: @fire_mage, count: 1, level_offset: 0, weight: 70} | {monster: @goblin_warrior, count: 2, level_offset: 3, weight: 30}</x:v>
+        <x:v>{monster: @Monster.fire_mage, count: 1, level_offset: 0, weight: 70} | {monster: @Monster.goblin_warrior, count: 2, level_offset: 3, weight: 30}</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>@drop_fire_mage</x:v>
+        <x:v>@DropTable.drop_fire_mage</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>SkillUnlockReward{key: first_clear_fireball, skill: @fireball, required_level: 12}</x:v>
+        <x:v>SkillUnlockReward{key: first_clear_fireball, skill: @Skill.fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>stamina: 12, time_limit: 420</x:v>
@@ -1837,7 +1883,7 @@
         <x:v>stage_dragon_peak</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>@stage_dragon_peak_name</x:v>
+        <x:v>@Text.stage_dragon_peak_name</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Raid</x:v>
@@ -1852,13 +1898,13 @@
         <x:v>{x: 61.0, y: 79.0} | {x: 80.0, y: 90.0}</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>{monster: @ancient_dragon, count: 1, level_offset: 0, weight: 100} | {monster: @fire_mage, count: 2, level_offset: 5, weight: 20}</x:v>
+        <x:v>{monster: @Monster.ancient_dragon, count: 1, level_offset: 0, weight: 100} | {monster: @Monster.fire_mage, count: 2, level_offset: 5, weight: 20}</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>@drop_ancient_dragon</x:v>
+        <x:v>@DropTable.drop_ancient_dragon</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>ItemReward{key: first_clear_dragon_scale, item: @dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: first_clear_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>stamina: 30, time_limit: 900, raid_size: 4</x:v>
@@ -1922,7 +1968,7 @@
         <x:v>Story</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>@quest_first_blade_title</x:v>
+        <x:v>@Text.quest_first_blade_title</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>First Blade</x:v>
@@ -1931,13 +1977,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>@stage_forest_road</x:v>
+        <x:v>@Stage.stage_forest_road</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>@goblin_warrior</x:v>
+        <x:v>@Monster.goblin_warrior</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>@iron_sword</x:v>
+        <x:v>@Equipment.iron_sword</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>_</x:v>
@@ -1946,7 +1992,7 @@
         <x:v>{key: defeat_goblins, target_count: 3, counters: {kill: 3, collect: 0}}</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>ItemReward{key: preview_first_blade, item: @iron_sword, count: 1}</x:v>
+        <x:v>ItemReward{key: preview_first_blade, item: @Equipment.iron_sword, count: 1}</x:v>
       </x:c>
       <x:c r="L2" t="str">
         <x:v>start_day: 1, end_day: 30</x:v>
@@ -1963,7 +2009,7 @@
         <x:v>Side</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>@quest_mage_trial_title</x:v>
+        <x:v>@Text.quest_mage_trial_title</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>Mage Trial</x:v>
@@ -1972,13 +2018,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>@stage_arcane_tower</x:v>
+        <x:v>@Stage.stage_arcane_tower</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>@fire_mage</x:v>
+        <x:v>@Monster.fire_mage</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>@flame_staff</x:v>
+        <x:v>@Equipment.flame_staff</x:v>
       </x:c>
       <x:c r="I3" t="str">
         <x:v>quest_first_blade</x:v>
@@ -1987,7 +2033,7 @@
         <x:v>{key: defeat_mage, target_count: 1, counters: {kill: 1}} | {key: collect_focus, target_count: 2, counters: {collect: 2, kill: 0}}</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>SkillUnlockReward{key: preview_mage_skill, skill: @fireball, required_level: 12}</x:v>
+        <x:v>SkillUnlockReward{key: preview_mage_skill, skill: @Skill.fireball, required_level: 12}</x:v>
       </x:c>
       <x:c r="L3" t="str">
         <x:v>start_day: 5, end_day: 45</x:v>
@@ -2004,7 +2050,7 @@
         <x:v>Raid</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>@quest_dragon_raid_title</x:v>
+        <x:v>@Text.quest_dragon_raid_title</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Dragon Raid</x:v>
@@ -2013,13 +2059,13 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>@stage_dragon_peak</x:v>
+        <x:v>@Stage.stage_dragon_peak</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>@ancient_dragon</x:v>
+        <x:v>@Monster.ancient_dragon</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>@dragon_scale</x:v>
+        <x:v>@Item.dragon_scale</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>quest_first_blade | quest_mage_trial</x:v>
@@ -2028,7 +2074,7 @@
         <x:v>{key: break_wings, target_count: 2, counters: {kill: 1, collect: 2}} | {key: survive_meteor, target_count: 1, counters: {kill: 1}}</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>ItemReward{key: preview_dragon_scale, item: @dragon_scale, count: 1}</x:v>
+        <x:v>ItemReward{key: preview_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>start_day: 20, end_day: 90</x:v>
@@ -2077,7 +2123,7 @@
         <x:v>shop_starter</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>@shop_starter_name</x:v>
+        <x:v>@Text.shop_starter_name</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>General</x:v>
@@ -2092,7 +2138,7 @@
         <x:v>_</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>{item: @healing_potion, price: 35, stock: 20, unlock_level: 1, required_quest: _, discount_by_day: {1: 0, 7: 10}} | {item: @iron_sword, price: 120, stock: 1, unlock_level: 1, required_quest: @quest_first_blade, discount_by_day: {1: 0}}</x:v>
+        <x:v>{item: @Item.healing_potion, price: 35, stock: 20, unlock_level: 1, required_quest: _, discount_by_day: {1: 0, 7: 10}} | {item: @Equipment.iron_sword, price: 120, stock: 1, unlock_level: 1, required_quest: @Quest.quest_first_blade, discount_by_day: {1: 0}}</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>gold</x:v>
@@ -2103,7 +2149,7 @@
         <x:v>shop_arcane</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>@shop_arcane_name</x:v>
+        <x:v>@Text.shop_arcane_name</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>Event</x:v>
@@ -2115,10 +2161,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>@stage_arcane_tower</x:v>
+        <x:v>@Stage.stage_arcane_tower</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>{item: @flame_staff, price: 760, stock: 1, unlock_level: 12, required_quest: @quest_mage_trial, discount_by_day: {1: 0, 14: 15}} | {item: @phoenix_feather, price: 1800, stock: 5, unlock_level: 18, required_quest: @quest_mage_trial, discount_by_day: {1: 0}}</x:v>
+        <x:v>{item: @Equipment.flame_staff, price: 760, stock: 1, unlock_level: 12, required_quest: @Quest.quest_mage_trial, discount_by_day: {1: 0, 14: 15}} | {item: @Item.phoenix_feather, price: 1800, stock: 5, unlock_level: 18, required_quest: @Quest.quest_mage_trial, discount_by_day: {1: 0}}</x:v>
       </x:c>
       <x:c r="H3" t="str">
         <x:v>gold | event_token</x:v>
@@ -2129,7 +2175,7 @@
         <x:v>shop_raid</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>@shop_raid_name</x:v>
+        <x:v>@Text.shop_raid_name</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Raid</x:v>
@@ -2141,10 +2187,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>@stage_dragon_peak</x:v>
+        <x:v>@Stage.stage_dragon_peak</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>{item: @dragon_scale, price: 5200, stock: 4, unlock_level: 45, required_quest: @quest_dragon_raid, discount_by_day: {1: 0}} | {item: @meteor_staff, price: 2600, stock: 1, unlock_level: 45, required_quest: @quest_dragon_raid, discount_by_day: {1: 0, 30: 20}}</x:v>
+        <x:v>{item: @Item.dragon_scale, price: 5200, stock: 4, unlock_level: 45, required_quest: @Quest.quest_dragon_raid, discount_by_day: {1: 0}} | {item: @Equipment.meteor_staff, price: 2600, stock: 1, unlock_level: 45, required_quest: @Quest.quest_dragon_raid, discount_by_day: {1: 0, 30: 20}}</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>gold | raid_token</x:v>

--- a/examples/rpg/data/rpg.xlsx
+++ b/examples/rpg/data/rpg.xlsx
@@ -2,16 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="R52dbdc023bce415c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf531816d5cf84605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R68e2e336839d48c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="R2d8088a070354357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="R0be2e9de3b2f4d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DropTable" sheetId="6" r:id="R3c95343529bf4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="7" r:id="R56856c5aa9744163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quest" sheetId="8" r:id="R2e2443ebd0524bb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop" sheetId="9" r:id="R15bab0945dcd4a52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="10" r:id="Rdf3710ed718843a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="1" r:id="Rb7cbc0639c1244cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7769ea97feba4da2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buff" sheetId="3" r:id="R296ef19d76494114"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="4" r:id="Rb566210011db4cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monster" sheetId="5" r:id="R9a0ba626eda14e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="6" r:id="Rd6964cd1ea5e4311"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -321,6 +317,9 @@
         <x:v>Upgrade Item ID</x:v>
       </x:c>
       <x:c r="M1" s="2" t="str">
+        <x:v>Featured Stage ID</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="str">
         <x:v>Legacy Power</x:v>
       </x:c>
     </x:row>
@@ -361,7 +360,10 @@
       <x:c r="L2" t="str">
         <x:v>_</x:v>
       </x:c>
-      <x:c r="M2" t="n">
+      <x:c r="M2" t="str">
+        <x:v>@Stage.stage_forest_road</x:v>
+      </x:c>
+      <x:c r="N2" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -402,7 +404,10 @@
       <x:c r="L3" t="str">
         <x:v>_</x:v>
       </x:c>
-      <x:c r="M3" t="n">
+      <x:c r="M3" t="str">
+        <x:v>@Stage.stage_arcane_tower</x:v>
+      </x:c>
+      <x:c r="N3" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -443,357 +448,11 @@
       <x:c r="L4" t="str">
         <x:v>_</x:v>
       </x:c>
-      <x:c r="M4" t="n">
+      <x:c r="M4" t="str">
+        <x:v>@Stage.stage_dragon_peak</x:v>
+      </x:c>
+      <x:c r="N4" t="n">
         <x:v>120</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>Text ID</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>ZH-CN</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>EN-US</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>Context</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>Max Length</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>Tags</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>item_iron_sword_name</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>铁剑</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Iron Sword</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>equipment name</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>item | equipment</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>item_flame_staff_name</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>焰火法杖</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Flame Staff</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>equipment name</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>item | equipment</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>item_meteor_staff_name</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>陨星法杖</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Meteor Staff</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>equipment name</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>item | equipment</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>item_dragon_guard_name</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>龙鳞护甲</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Dragon Guard</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>equipment name</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>item | equipment</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>buff_burning_name</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>燃烧</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Burning</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>buff name</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>buff | combat</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>buff_battle_focus_name</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>战斗专注</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Battle Focus</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>buff name</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>buff | combat</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>buff_meteor_mark_name</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>陨星印记</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Meteor Mark</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>buff name</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>buff | raid</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>stage_forest_road_name</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>林地道路</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Forest Road</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>stage name</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>stage | story</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>stage_arcane_tower_name</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>秘法高塔</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Arcane Tower</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>stage name</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>stage | elite</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>stage_dragon_peak_name</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>龙巢峰顶</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Dragon Peak</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>stage name</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>stage | raid</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>quest_first_blade_title</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>第一把剑</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>First Blade</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>quest title</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>quest | story</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>quest_mage_trial_title</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>法师试炼</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Mage Trial</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>quest title</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>quest | side</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>quest_dragon_raid_title</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>巨龙讨伐</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>Dragon Raid</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>quest title</x:v>
-      </x:c>
-      <x:c r="E14" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>quest | raid</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>shop_starter_name</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>新手补给</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>Starter Supply</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>shop name</x:v>
-      </x:c>
-      <x:c r="E15" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>shop | general</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
-        <x:v>shop_arcane_name</x:v>
-      </x:c>
-      <x:c r="B16" t="str">
-        <x:v>秘法商店</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>Arcane Shop</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>shop name</x:v>
-      </x:c>
-      <x:c r="E16" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>shop | event</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>shop_raid_name</x:v>
-      </x:c>
-      <x:c r="B17" t="str">
-        <x:v>讨伐补给</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>Raid Supply</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>shop name</x:v>
-      </x:c>
-      <x:c r="E17" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>shop | raid</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -846,21 +505,24 @@
         <x:v>Upgrade Item ID</x:v>
       </x:c>
       <x:c r="N1" s="2" t="str">
+        <x:v>Featured Stage ID</x:v>
+      </x:c>
+      <x:c r="O1" s="2" t="str">
         <x:v>Legacy Power</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="str">
+      <x:c r="P1" s="2" t="str">
         <x:v>Required Class</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="str">
+      <x:c r="Q1" s="2" t="str">
         <x:v>Stat Bonus</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="str">
+      <x:c r="R1" s="2" t="str">
         <x:v>Allowed Classes</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="str">
+      <x:c r="S1" s="2" t="str">
         <x:v>Upgrade Costs</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="str">
+      <x:c r="T1" s="2" t="str">
         <x:v>Set Piece ID</x:v>
       </x:c>
     </x:row>
@@ -904,22 +566,25 @@
       <x:c r="M2" t="str">
         <x:v>@Equipment.flame_staff</x:v>
       </x:c>
-      <x:c r="N2" t="n">
+      <x:c r="N2" t="str">
+        <x:v>@Stage.stage_forest_road</x:v>
+      </x:c>
+      <x:c r="O2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="O2" t="str">
+      <x:c r="P2" t="str">
         <x:v>warrior</x:v>
       </x:c>
-      <x:c r="P2" t="str">
+      <x:c r="Q2" t="str">
         <x:v>hp: 10, attack: 12, defense: 2, speed: 1.0, crit: 5</x:v>
       </x:c>
-      <x:c r="Q2" t="str">
+      <x:c r="R2" t="str">
         <x:v>warrior | ranger</x:v>
       </x:c>
-      <x:c r="R2" t="str">
+      <x:c r="S2" t="str">
         <x:v>1: 40, 2: 80, 3: 160</x:v>
       </x:c>
-      <x:c r="S2" t="str">
+      <x:c r="T2" t="str">
         <x:v>_</x:v>
       </x:c>
     </x:row>
@@ -963,22 +628,25 @@
       <x:c r="M3" t="str">
         <x:v>@Equipment.meteor_staff</x:v>
       </x:c>
-      <x:c r="N3" t="n">
+      <x:c r="N3" t="str">
+        <x:v>@Stage.stage_arcane_tower</x:v>
+      </x:c>
+      <x:c r="O3" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="O3" t="str">
+      <x:c r="P3" t="str">
         <x:v>mage</x:v>
       </x:c>
-      <x:c r="P3" t="str">
+      <x:c r="Q3" t="str">
         <x:v>hp: 12, attack: 48, defense: 4, speed: 0.9, crit: 8</x:v>
       </x:c>
-      <x:c r="Q3" t="str">
+      <x:c r="R3" t="str">
         <x:v>mage | scholar</x:v>
       </x:c>
-      <x:c r="R3" t="str">
+      <x:c r="S3" t="str">
         <x:v>1: 120, 2: 240, 3: 480</x:v>
       </x:c>
-      <x:c r="S3" t="str">
+      <x:c r="T3" t="str">
         <x:v>_</x:v>
       </x:c>
     </x:row>
@@ -1022,22 +690,25 @@
       <x:c r="M4" t="str">
         <x:v>_</x:v>
       </x:c>
-      <x:c r="N4" t="n">
+      <x:c r="N4" t="str">
+        <x:v>@Stage.stage_dragon_peak</x:v>
+      </x:c>
+      <x:c r="O4" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="O4" t="str">
+      <x:c r="P4" t="str">
         <x:v>mage</x:v>
       </x:c>
-      <x:c r="P4" t="str">
+      <x:c r="Q4" t="str">
         <x:v>hp: 40, attack: 96, defense: 18, speed: 0.8, crit: 18</x:v>
       </x:c>
-      <x:c r="Q4" t="str">
+      <x:c r="R4" t="str">
         <x:v>mage | scholar</x:v>
       </x:c>
-      <x:c r="R4" t="str">
+      <x:c r="S4" t="str">
         <x:v>1: 300, 2: 600, 3: 900</x:v>
       </x:c>
-      <x:c r="S4" t="str">
+      <x:c r="T4" t="str">
         <x:v>_</x:v>
       </x:c>
     </x:row>
@@ -1081,22 +752,25 @@
       <x:c r="M5" t="str">
         <x:v>_</x:v>
       </x:c>
-      <x:c r="N5" t="n">
+      <x:c r="N5" t="str">
+        <x:v>@Stage.stage_dragon_peak</x:v>
+      </x:c>
+      <x:c r="O5" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="O5" t="str">
+      <x:c r="P5" t="str">
         <x:v>warrior</x:v>
       </x:c>
-      <x:c r="P5" t="str">
+      <x:c r="Q5" t="str">
         <x:v>hp: 220, attack: 12, defense: 160, speed: 0.7, crit: 4</x:v>
       </x:c>
-      <x:c r="Q5" t="str">
+      <x:c r="R5" t="str">
         <x:v>warrior | guardian</x:v>
       </x:c>
-      <x:c r="R5" t="str">
+      <x:c r="S5" t="str">
         <x:v>1: 500, 2: 750, 3: 950</x:v>
       </x:c>
-      <x:c r="S5" t="str">
+      <x:c r="T5" t="str">
         <x:v>@Equipment.iron_sword</x:v>
       </x:c>
     </x:row>
@@ -1659,541 +1333,342 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>Drop ID</x:v>
+        <x:v>Text ID</x:v>
       </x:c>
       <x:c r="B1" s="2" t="str">
-        <x:v>Monster ID</x:v>
+        <x:v>ZH-CN</x:v>
       </x:c>
       <x:c r="C1" s="2" t="str">
-        <x:v>Conditions</x:v>
+        <x:v>EN-US</x:v>
       </x:c>
       <x:c r="D1" s="2" t="str">
-        <x:v>Rewards</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="E1" s="2" t="str">
-        <x:v>Weights</x:v>
+        <x:v>Max Length</x:v>
       </x:c>
       <x:c r="F1" s="2" t="str">
-        <x:v>Bonus By Rarity</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>Currency Curve</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="str">
-        <x:v>Guaranteed Reward</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="str">
-        <x:v>Notes</x:v>
+        <x:v>Tags</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
-        <x:v>drop_goblin_warrior</x:v>
+        <x:v>item_iron_sword_name</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>@Monster.goblin_warrior</x:v>
+        <x:v>铁剑</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>min_level: 1, required_element: Physical, flags: Damage</x:v>
+        <x:v>Iron Sword</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>ItemReward{key: reward_goblin_sword, item: @Equipment.iron_sword, count: 1} | CurrencyReward{key: reward_goblin_gold, count: 1, currency: gold, amount: 35}</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>70 | 30</x:v>
+        <x:v>equipment name</x:v>
+      </x:c>
+      <x:c r="E2" t="n">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>Common: 0, Rare: 5</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>1: 10, 5: 20</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>CurrencyReward{key: guaranteed_goblin_gold, count: 1, currency: gold, amount: 5}</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>tutorial | melee</x:v>
+        <x:v>item | equipment</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>drop_fire_mage</x:v>
+        <x:v>item_flame_staff_name</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>@Monster.fire_mage</x:v>
+        <x:v>焰火法杖</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>min_level: 12, required_element: Fire, flags: Damage</x:v>
+        <x:v>Flame Staff</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>ItemReward{key: reward_mage_staff, item: @Equipment.flame_staff, count: 1} | CurrencyReward{key: reward_mage_gold, count: 1, currency: gold, amount: 120} | SkillUnlockReward{key: reward_mage_skill, skill: @Skill.fireball, required_level: 12}</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>25 | 65 | 10</x:v>
+        <x:v>equipment name</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>Common: 0, Rare: 15, Epic: 30</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>1: 25, 18: 90</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>ItemReward{key: guaranteed_mage_staff, item: @Equipment.flame_staff, count: 1}</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>caster | fire</x:v>
+        <x:v>item | equipment</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>drop_ancient_dragon</x:v>
+        <x:v>item_meteor_staff_name</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>@Monster.ancient_dragon</x:v>
+        <x:v>陨星法杖</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>min_level: 45, required_element: Fire, flags: Ultimate</x:v>
+        <x:v>Meteor Staff</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>ItemReward{key: reward_dragon_feather, item: @Item.phoenix_feather, count: 2} | CurrencyReward{key: reward_dragon_gold, count: 1, currency: gold, amount: 1000} | SkillUnlockReward{key: reward_dragon_meteor, skill: @Skill.meteor, required_level: 45}</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>40 | 45 | 15</x:v>
+        <x:v>equipment name</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>Common: 0, Rare: 30, Epic: 80, Legendary: 120</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>1: 100, 50: 900</x:v>
-      </x:c>
-      <x:c r="H4" t="str">
-        <x:v>ItemReward{key: guaranteed_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
-      </x:c>
-      <x:c r="I4" t="str">
-        <x:v>raid | dragon | endgame</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>Stage ID</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>Name Text ID</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>Kind</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>Unlock Level</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>Recommended Power</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>Positions</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>Spawns</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="str">
-        <x:v>Drop Table ID</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="str">
-        <x:v>First Clear Reward</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="str">
-        <x:v>Modifiers</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>stage_forest_road</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>@Text.stage_forest_road_name</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Story</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>{x: 9.0, y: 4.0}</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>{monster: @Monster.goblin_warrior, count: 3, level_offset: 0, weight: 100}</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>@DropTable.drop_goblin_warrior</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>ItemReward{key: first_clear_forest_blade, item: @Equipment.iron_sword, count: 1}</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>stamina: 6, time_limit: 300</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>stage_arcane_tower</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>@Text.stage_arcane_tower_name</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Elite</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>{x: 20.0, y: -7.0} | {x: 25.0, y: -9.0}</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>{monster: @Monster.fire_mage, count: 1, level_offset: 0, weight: 70} | {monster: @Monster.goblin_warrior, count: 2, level_offset: 3, weight: 30}</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>@DropTable.drop_fire_mage</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>SkillUnlockReward{key: first_clear_fireball, skill: @Skill.fireball, required_level: 12}</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>stamina: 12, time_limit: 420</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>stage_dragon_peak</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>@Text.stage_dragon_peak_name</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Raid</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>{x: 61.0, y: 79.0} | {x: 80.0, y: 90.0}</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>{monster: @Monster.ancient_dragon, count: 1, level_offset: 0, weight: 100} | {monster: @Monster.fire_mage, count: 2, level_offset: 5, weight: 20}</x:v>
-      </x:c>
-      <x:c r="H4" t="str">
-        <x:v>@DropTable.drop_ancient_dragon</x:v>
-      </x:c>
-      <x:c r="I4" t="str">
-        <x:v>ItemReward{key: first_clear_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>stamina: 30, time_limit: 900, raid_size: 4</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>Quest ID</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>Kind</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>Title Text ID</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>Title</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>Min Level</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>Stage ID</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>Target Monster ID</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="str">
-        <x:v>Reward Item ID</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="str">
-        <x:v>Prerequisites</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="str">
-        <x:v>Objectives</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="str">
-        <x:v>Reward Preview</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="str">
-        <x:v>Availability</x:v>
-      </x:c>
-      <x:c r="M1" s="2" t="str">
-        <x:v>Dialogue</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>quest_first_blade</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>Story</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>@Text.quest_first_blade_title</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
+        <x:v>item | equipment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>item_dragon_guard_name</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>龙鳞护甲</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Dragon Guard</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>equipment name</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>item | equipment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>buff_burning_name</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>燃烧</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Burning</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>buff name</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>buff | combat</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>buff_battle_focus_name</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>战斗专注</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Battle Focus</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>buff name</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>buff | combat</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>buff_meteor_mark_name</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>陨星印记</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Meteor Mark</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>buff name</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>buff | raid</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>stage_forest_road_name</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>林地道路</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Forest Road</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>stage name</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>stage | story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>stage_arcane_tower_name</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>秘法高塔</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Arcane Tower</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>stage name</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>stage | elite</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>stage_dragon_peak_name</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>龙巢峰顶</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Dragon Peak</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>stage name</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>stage | raid</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>quest_first_blade_title</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>第一把剑</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
         <x:v>First Blade</x:v>
       </x:c>
-      <x:c r="E2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>@Stage.stage_forest_road</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>@Monster.goblin_warrior</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>@Equipment.iron_sword</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>_</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>{key: defeat_goblins, target_count: 3, counters: {kill: 3, collect: 0}}</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>ItemReward{key: preview_first_blade, item: @Equipment.iron_sword, count: 1}</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>start_day: 1, end_day: 30</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>key: root, text: "Clear the road.", next: [{key: accept, text: "I will handle it."} | {key: decline, text: "Later."}]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>quest_mage_trial</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>Side</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>@Text.quest_mage_trial_title</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="D12" t="str">
+        <x:v>quest title</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>quest | story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>quest_mage_trial_title</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>法师试炼</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
         <x:v>Mage Trial</x:v>
       </x:c>
-      <x:c r="E3" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>@Stage.stage_arcane_tower</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>@Monster.fire_mage</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>@Equipment.flame_staff</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>quest_first_blade</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>{key: defeat_mage, target_count: 1, counters: {kill: 1}} | {key: collect_focus, target_count: 2, counters: {collect: 2, kill: 0}}</x:v>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>SkillUnlockReward{key: preview_mage_skill, skill: @Skill.fireball, required_level: 12}</x:v>
-      </x:c>
-      <x:c r="L3" t="str">
-        <x:v>start_day: 5, end_day: 45</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>key: root, text: "Prove your focus.", next: [{key: teach, text: "Show me the spell."}]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>quest_dragon_raid</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>Raid</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>@Text.quest_dragon_raid_title</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D13" t="str">
+        <x:v>quest title</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>quest | side</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>quest_dragon_raid_title</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>巨龙讨伐</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
         <x:v>Dragon Raid</x:v>
       </x:c>
-      <x:c r="E4" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>@Stage.stage_dragon_peak</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>@Monster.ancient_dragon</x:v>
-      </x:c>
-      <x:c r="H4" t="str">
-        <x:v>@Item.dragon_scale</x:v>
-      </x:c>
-      <x:c r="I4" t="str">
-        <x:v>quest_first_blade | quest_mage_trial</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>{key: break_wings, target_count: 2, counters: {kill: 1, collect: 2}} | {key: survive_meteor, target_count: 1, counters: {kill: 1}}</x:v>
-      </x:c>
-      <x:c r="K4" t="str">
-        <x:v>ItemReward{key: preview_dragon_scale, item: @Item.dragon_scale, count: 1}</x:v>
-      </x:c>
-      <x:c r="L4" t="str">
-        <x:v>start_day: 20, end_day: 90</x:v>
-      </x:c>
-      <x:c r="M4" t="str">
-        <x:v>key: root, text: "The peak is burning.", next: [{key: rally, text: "Gather the raid."} | {key: scout, text: "Find a safer path.", next: [{key: report, text: "Return before dawn."}]}]</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>Shop ID</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>Name Text ID</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>Kind</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>Open Day</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>Close Day</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>Stage Gate ID</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>Entries</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="str">
-        <x:v>Currencies</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>shop_starter</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>@Text.shop_starter_name</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>General</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>_</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>{item: @Item.healing_potion, price: 35, stock: 20, unlock_level: 1, required_quest: _, discount_by_day: {1: 0, 7: 10}} | {item: @Equipment.iron_sword, price: 120, stock: 1, unlock_level: 1, required_quest: @Quest.quest_first_blade, discount_by_day: {1: 0}}</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>gold</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>shop_arcane</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>@Text.shop_arcane_name</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Event</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>@Stage.stage_arcane_tower</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>{item: @Equipment.flame_staff, price: 760, stock: 1, unlock_level: 12, required_quest: @Quest.quest_mage_trial, discount_by_day: {1: 0, 14: 15}} | {item: @Item.phoenix_feather, price: 1800, stock: 5, unlock_level: 18, required_quest: @Quest.quest_mage_trial, discount_by_day: {1: 0}}</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>gold | event_token</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>shop_raid</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>@Text.shop_raid_name</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Raid</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>@Stage.stage_dragon_peak</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>{item: @Item.dragon_scale, price: 5200, stock: 4, unlock_level: 45, required_quest: @Quest.quest_dragon_raid, discount_by_day: {1: 0}} | {item: @Equipment.meteor_staff, price: 2600, stock: 1, unlock_level: 45, required_quest: @Quest.quest_dragon_raid, discount_by_day: {1: 0, 30: 20}}</x:v>
-      </x:c>
-      <x:c r="H4" t="str">
-        <x:v>gold | raid_token</x:v>
+      <x:c r="D14" t="str">
+        <x:v>quest title</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>quest | raid</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>shop_starter_name</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>新手补给</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Starter Supply</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>shop name</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>shop | general</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>shop_arcane_name</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>秘法商店</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Arcane Shop</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>shop name</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>shop | event</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>shop_raid_name</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>讨伐补给</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Raid Supply</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>shop name</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>shop | raid</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/examples/rpg/data/rpg.xlsx
+++ b/examples/rpg/data/rpg.xlsx
@@ -450,7 +450,7 @@
     <t>Weapon | Armor</t>
   </si>
   <si>
-    <t>shape: cone, params: {range: 2.0, angle: 90.0}</t>
+    <t>shape: cone, parameters: {range: 2.0, angle: 90.0}</t>
   </si>
   <si>
     <t>fireball</t>
@@ -471,7 +471,7 @@
     <t>Weapon | Accessory</t>
   </si>
   <si>
-    <t>shape: circle, params: {range: 8.0, radius: 2.5}</t>
+    <t>shape: circle, parameters: {range: 8.0, radius: 2.5}</t>
   </si>
   <si>
     <t>meteor</t>
@@ -489,7 +489,7 @@
     <t>0 | 50 | 100</t>
   </si>
   <si>
-    <t>shape: circle, params: {range: 12.0, radius: 5.0}</t>
+    <t>shape: circle, parameters: {range: 12.0, radius: 5.0}</t>
   </si>
   <si>
     <t>battle_trance</t>
@@ -504,7 +504,7 @@
     <t>0 | 5 | 10</t>
   </si>
   <si>
-    <t>shape: self, params: {range: 0.0, duration: 12.0}</t>
+    <t>shape: self, parameters: {range: 0.0, duration: 12.0}</t>
   </si>
   <si>
     <t>Monster ID</t>
